--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs - VENTAS/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="963" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82EBABF7-3A83-433A-863F-E78944A9487D}"/>
+  <xr:revisionPtr revIDLastSave="987" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E38304-6548-49C6-9C14-301029E4E02E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -533,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -2684,8 +2684,135 @@
         <v>55650</v>
       </c>
     </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+    </row>
+    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+    </row>
+    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+    </row>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+    </row>
+    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+    </row>
+    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+    </row>
+    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E126" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E151" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="987" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E38304-6548-49C6-9C14-301029E4E02E}"/>
+  <xr:revisionPtr revIDLastSave="1001" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CD8210E-7EAE-46FE-9BCC-A78E6EBC242D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -570,7 +570,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>1500</v>
+        <v>848</v>
       </c>
       <c r="E2" s="2">
         <v>3000</v>
@@ -825,7 +825,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E17" s="2">
         <v>1500</v>
@@ -910,7 +910,7 @@
         <v>22</v>
       </c>
       <c r="D22" s="2">
-        <v>1200</v>
+        <v>417</v>
       </c>
       <c r="E22" s="2">
         <v>1450</v>
@@ -1420,7 +1420,7 @@
         <v>22</v>
       </c>
       <c r="D52" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="2">
         <v>2000</v>
@@ -1505,7 +1505,7 @@
         <v>22</v>
       </c>
       <c r="D57" s="2">
-        <v>1200</v>
+        <v>835</v>
       </c>
       <c r="E57" s="2">
         <v>1100</v>
@@ -1675,7 +1675,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="2">
-        <v>1200</v>
+        <v>1043</v>
       </c>
       <c r="E67" s="2">
         <v>1800</v>
@@ -1845,7 +1845,7 @@
         <v>22</v>
       </c>
       <c r="D77" s="2">
-        <v>1500</v>
+        <v>848</v>
       </c>
       <c r="E77" s="2">
         <v>2850</v>
@@ -2270,7 +2270,7 @@
         <v>22</v>
       </c>
       <c r="D102" s="2">
-        <v>1500</v>
+        <v>913</v>
       </c>
       <c r="E102" s="2">
         <v>2600</v>
@@ -2525,7 +2525,7 @@
         <v>22</v>
       </c>
       <c r="D117" s="2">
-        <v>27700</v>
+        <v>25304</v>
       </c>
       <c r="E117" s="2">
         <v>55650</v>
@@ -2610,7 +2610,7 @@
         <v>22</v>
       </c>
       <c r="D122" s="2">
-        <v>27700</v>
+        <v>25304</v>
       </c>
       <c r="E122" s="2">
         <v>55650</v>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1001" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CD8210E-7EAE-46FE-9BCC-A78E6EBC242D}"/>
+  <xr:revisionPtr revIDLastSave="1012" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BB84383-6366-441F-A1D7-B1EDC7758D80}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
